--- a/data/processed/positivacao/2024-04_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2024-04_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25725,7 +25725,7 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B977" t="inlineStr"/>
@@ -36817,7 +36817,7 @@
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr"/>
@@ -65501,7 +65501,7 @@
     <row r="2508">
       <c r="A2508" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2508" t="inlineStr"/>
@@ -67172,7 +67172,7 @@
       <c r="A2573" t="inlineStr"/>
       <c r="B2573" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 1 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 375,78</t>
+          <t>Vendedor 1 - VENDEDOR 01: positivou 1 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 375,78</t>
         </is>
       </c>
       <c r="C2573" t="inlineStr"/>
@@ -67189,10 +67189,10 @@
       <c r="B2574" t="inlineStr">
         <is>
           <t xml:space="preserve">Vendedor 18 - LOJA: positivou 154 cliente(s), não positivou 726 cliente(s) - Total vendido: R$ 52.744,18
-Vendedor 3 - FERNANDA: positivou 89 cliente(s), não positivou 337 cliente(s) - Total vendido: R$ 120.754,17
-Vendedor 4 - DANIELA: positivou 88 cliente(s), não positivou 566 cliente(s) - Total vendido: R$ 41.027,10
+Vendedor 3 - VENDEDOR 03: positivou 89 cliente(s), não positivou 337 cliente(s) - Total vendido: R$ 120.754,17
+Vendedor 4 - VENDEDOR 04: positivou 88 cliente(s), não positivou 566 cliente(s) - Total vendido: R$ 41.027,10
 Vendedor 5 - SITE: positivou 4 cliente(s), não positivou 444 cliente(s) - Total vendido: R$ 316,61
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00
  </t>
         </is>
       </c>
